--- a/docs/test-cases-2026-08-20.xlsx
+++ b/docs/test-cases-2026-08-20.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ngantran\source\repos\ecomerce\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74692222-6807-40FD-AED0-6D70C432B23B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46E2D11D-F231-4AA1-AA98-609674BC566F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Basket!$A$1:$K$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">Common!$A$1:$K$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6">Common!$A$1:$K$98</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Gateway!$A$1:$K$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Order!$A$1:$K$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Party!$A$1:$K$9</definedName>
@@ -10113,7 +10113,6 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:K98"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -10123,9 +10122,9 @@
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="56" customWidth="1"/>
-    <col min="7" max="9" width="50" customWidth="1"/>
-    <col min="10" max="10" width="62" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="7" max="7" width="62" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="11" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="32" customHeight="1" x14ac:dyDescent="0.35">
@@ -10148,22 +10147,22 @@
         <v>27</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>776</v>
       </c>
@@ -10183,22 +10182,22 @@
         <v>778</v>
       </c>
       <c r="G2" s="6" t="s">
+        <v>782</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>779</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="J2" s="6" t="s">
         <v>780</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="K2" s="6" t="s">
         <v>781</v>
       </c>
-      <c r="J2" s="6" t="s">
-        <v>782</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>783</v>
       </c>
@@ -10218,22 +10217,22 @@
         <v>784</v>
       </c>
       <c r="G3" s="6" t="s">
+        <v>782</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>785</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>786</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="K3" s="6" t="s">
         <v>787</v>
       </c>
-      <c r="J3" s="6" t="s">
-        <v>782</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>788</v>
       </c>
@@ -10253,22 +10252,22 @@
         <v>789</v>
       </c>
       <c r="G4" s="6" t="s">
+        <v>782</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" s="6" t="s">
         <v>790</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="J4" s="6" t="s">
         <v>786</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="K4" s="6" t="s">
         <v>791</v>
       </c>
-      <c r="J4" s="6" t="s">
-        <v>782</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>792</v>
       </c>
@@ -10288,22 +10287,22 @@
         <v>794</v>
       </c>
       <c r="G5" s="6" t="s">
+        <v>798</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>795</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="J5" s="6" t="s">
         <v>796</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="K5" s="6" t="s">
         <v>797</v>
       </c>
-      <c r="J5" s="6" t="s">
-        <v>798</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>799</v>
       </c>
@@ -10323,22 +10322,22 @@
         <v>800</v>
       </c>
       <c r="G6" s="6" t="s">
+        <v>798</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>801</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="J6" s="6" t="s">
         <v>802</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="K6" s="6" t="s">
         <v>803</v>
       </c>
-      <c r="J6" s="6" t="s">
-        <v>798</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>804</v>
       </c>
@@ -10358,22 +10357,22 @@
         <v>805</v>
       </c>
       <c r="G7" s="6" t="s">
+        <v>798</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>806</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="J7" s="6" t="s">
         <v>807</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="K7" s="6" t="s">
         <v>808</v>
       </c>
-      <c r="J7" s="6" t="s">
-        <v>798</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>809</v>
       </c>
@@ -10393,22 +10392,22 @@
         <v>810</v>
       </c>
       <c r="G8" s="6" t="s">
+        <v>798</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>811</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="J8" s="6" t="s">
         <v>812</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="K8" s="6" t="s">
         <v>813</v>
       </c>
-      <c r="J8" s="6" t="s">
-        <v>798</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>814</v>
       </c>
@@ -10428,22 +10427,22 @@
         <v>815</v>
       </c>
       <c r="G9" s="6" t="s">
+        <v>798</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I9" s="6" t="s">
         <v>816</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="J9" s="6" t="s">
         <v>817</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="K9" s="6" t="s">
         <v>818</v>
       </c>
-      <c r="J9" s="6" t="s">
-        <v>798</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>819</v>
       </c>
@@ -10463,22 +10462,22 @@
         <v>820</v>
       </c>
       <c r="G10" s="6" t="s">
+        <v>798</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" s="6" t="s">
         <v>821</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="J10" s="6" t="s">
         <v>822</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="K10" s="6" t="s">
         <v>823</v>
       </c>
-      <c r="J10" s="6" t="s">
-        <v>798</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>824</v>
       </c>
@@ -10498,19 +10497,19 @@
         <v>825</v>
       </c>
       <c r="G11" s="6" t="s">
+        <v>798</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I11" s="6" t="s">
         <v>826</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="J11" s="6" t="s">
         <v>827</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="K11" s="6" t="s">
         <v>828</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>798</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -10533,19 +10532,19 @@
         <v>831</v>
       </c>
       <c r="G12" s="6" t="s">
+        <v>835</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I12" s="6" t="s">
         <v>832</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="J12" s="6" t="s">
         <v>833</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="K12" s="6" t="s">
         <v>834</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>835</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -10568,19 +10567,19 @@
         <v>837</v>
       </c>
       <c r="G13" s="6" t="s">
+        <v>835</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I13" s="6" t="s">
         <v>838</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="J13" s="6" t="s">
         <v>839</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="K13" s="6" t="s">
         <v>840</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>835</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -10603,19 +10602,19 @@
         <v>842</v>
       </c>
       <c r="G14" s="6" t="s">
+        <v>835</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I14" s="6" t="s">
         <v>843</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="J14" s="6" t="s">
         <v>844</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="K14" s="6" t="s">
         <v>845</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>835</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -10638,19 +10637,19 @@
         <v>159</v>
       </c>
       <c r="G15" s="6" t="s">
+        <v>835</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I15" s="6" t="s">
         <v>847</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="J15" s="6" t="s">
         <v>848</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="K15" s="6" t="s">
         <v>849</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>835</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -10673,19 +10672,19 @@
         <v>851</v>
       </c>
       <c r="G16" s="6" t="s">
+        <v>835</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I16" s="6" t="s">
         <v>852</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="J16" s="6" t="s">
         <v>844</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="K16" s="6" t="s">
         <v>853</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>835</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
@@ -10708,19 +10707,19 @@
         <v>61</v>
       </c>
       <c r="G17" s="6" t="s">
+        <v>835</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I17" s="6" t="s">
         <v>855</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="J17" s="6" t="s">
         <v>844</v>
       </c>
-      <c r="I17" s="6" t="s">
+      <c r="K17" s="6" t="s">
         <v>531</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>835</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -10743,19 +10742,19 @@
         <v>858</v>
       </c>
       <c r="G18" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I18" s="6" t="s">
         <v>859</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="J18" s="6" t="s">
         <v>860</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="K18" s="6" t="s">
         <v>861</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>862</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -10778,19 +10777,19 @@
         <v>864</v>
       </c>
       <c r="G19" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I19" s="6" t="s">
         <v>865</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="J19" s="6" t="s">
         <v>860</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="K19" s="6" t="s">
         <v>866</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>862</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -10813,19 +10812,19 @@
         <v>869</v>
       </c>
       <c r="G20" s="6" t="s">
+        <v>873</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I20" s="6" t="s">
         <v>870</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="J20" s="6" t="s">
         <v>871</v>
       </c>
-      <c r="I20" s="6" t="s">
+      <c r="K20" s="6" t="s">
         <v>872</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>873</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -10848,19 +10847,19 @@
         <v>875</v>
       </c>
       <c r="G21" s="6" t="s">
+        <v>873</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I21" s="6" t="s">
         <v>876</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="J21" s="6" t="s">
         <v>877</v>
       </c>
-      <c r="I21" s="6" t="s">
+      <c r="K21" s="6" t="s">
         <v>878</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>873</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
@@ -10883,19 +10882,19 @@
         <v>880</v>
       </c>
       <c r="G22" s="6" t="s">
+        <v>873</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I22" s="6" t="s">
         <v>881</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="J22" s="6" t="s">
         <v>882</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="K22" s="6" t="s">
         <v>883</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>873</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -10918,19 +10917,19 @@
         <v>885</v>
       </c>
       <c r="G23" s="6" t="s">
+        <v>873</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I23" s="6" t="s">
         <v>886</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="J23" s="6" t="s">
         <v>871</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="K23" s="6" t="s">
         <v>887</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>873</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -10953,19 +10952,19 @@
         <v>889</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>873</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I24" s="6" t="s">
         <v>881</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="J24" s="6" t="s">
         <v>890</v>
       </c>
-      <c r="I24" s="6" t="s">
+      <c r="K24" s="6" t="s">
         <v>891</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>873</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -10988,19 +10987,19 @@
         <v>893</v>
       </c>
       <c r="G25" s="6" t="s">
+        <v>873</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I25" s="6" t="s">
         <v>894</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="J25" s="6" t="s">
         <v>895</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="K25" s="6" t="s">
         <v>896</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>873</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -11023,19 +11022,19 @@
         <v>899</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>903</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I26" s="6" t="s">
         <v>900</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="J26" s="6" t="s">
         <v>901</v>
       </c>
-      <c r="I26" s="6" t="s">
+      <c r="K26" s="6" t="s">
         <v>902</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>903</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -11058,19 +11057,19 @@
         <v>905</v>
       </c>
       <c r="G27" s="6" t="s">
+        <v>903</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I27" s="6" t="s">
         <v>906</v>
       </c>
-      <c r="H27" s="6" t="s">
+      <c r="J27" s="6" t="s">
         <v>901</v>
       </c>
-      <c r="I27" s="6" t="s">
+      <c r="K27" s="6" t="s">
         <v>907</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>903</v>
-      </c>
-      <c r="K27" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
@@ -11093,19 +11092,19 @@
         <v>909</v>
       </c>
       <c r="G28" s="6" t="s">
+        <v>903</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I28" s="6" t="s">
         <v>910</v>
       </c>
-      <c r="H28" s="6" t="s">
+      <c r="J28" s="6" t="s">
         <v>911</v>
       </c>
-      <c r="I28" s="6" t="s">
+      <c r="K28" s="6" t="s">
         <v>912</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>903</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
@@ -11128,19 +11127,19 @@
         <v>914</v>
       </c>
       <c r="G29" s="6" t="s">
+        <v>903</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I29" s="6" t="s">
         <v>910</v>
       </c>
-      <c r="H29" s="6" t="s">
+      <c r="J29" s="6" t="s">
         <v>915</v>
       </c>
-      <c r="I29" s="6" t="s">
+      <c r="K29" s="6" t="s">
         <v>916</v>
-      </c>
-      <c r="J29" s="6" t="s">
-        <v>903</v>
-      </c>
-      <c r="K29" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
@@ -11163,19 +11162,19 @@
         <v>918</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>903</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I30" s="6" t="s">
         <v>919</v>
       </c>
-      <c r="H30" s="6" t="s">
+      <c r="J30" s="6" t="s">
         <v>920</v>
       </c>
-      <c r="I30" s="6" t="s">
+      <c r="K30" s="6" t="s">
         <v>921</v>
-      </c>
-      <c r="J30" s="6" t="s">
-        <v>903</v>
-      </c>
-      <c r="K30" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
@@ -11198,19 +11197,19 @@
         <v>923</v>
       </c>
       <c r="G31" s="6" t="s">
+        <v>903</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I31" s="6" t="s">
         <v>924</v>
       </c>
-      <c r="H31" s="6" t="s">
+      <c r="J31" s="6" t="s">
         <v>901</v>
       </c>
-      <c r="I31" s="6" t="s">
+      <c r="K31" s="6" t="s">
         <v>925</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>903</v>
-      </c>
-      <c r="K31" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
@@ -11233,19 +11232,19 @@
         <v>928</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>932</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I32" s="6" t="s">
         <v>929</v>
       </c>
-      <c r="H32" s="6" t="s">
+      <c r="J32" s="6" t="s">
         <v>930</v>
       </c>
-      <c r="I32" s="6" t="s">
+      <c r="K32" s="6" t="s">
         <v>931</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>932</v>
-      </c>
-      <c r="K32" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -11268,19 +11267,19 @@
         <v>934</v>
       </c>
       <c r="G33" s="6" t="s">
+        <v>932</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I33" s="6" t="s">
         <v>935</v>
       </c>
-      <c r="H33" s="6" t="s">
+      <c r="J33" s="6" t="s">
         <v>936</v>
       </c>
-      <c r="I33" s="6" t="s">
+      <c r="K33" s="6" t="s">
         <v>937</v>
-      </c>
-      <c r="J33" s="6" t="s">
-        <v>932</v>
-      </c>
-      <c r="K33" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -11303,19 +11302,19 @@
         <v>939</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>932</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I34" s="6" t="s">
         <v>940</v>
       </c>
-      <c r="H34" s="6" t="s">
+      <c r="J34" s="6" t="s">
         <v>936</v>
       </c>
-      <c r="I34" s="6" t="s">
+      <c r="K34" s="6" t="s">
         <v>941</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>932</v>
-      </c>
-      <c r="K34" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -11338,19 +11337,19 @@
         <v>943</v>
       </c>
       <c r="G35" s="6" t="s">
+        <v>932</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I35" s="6" t="s">
         <v>944</v>
       </c>
-      <c r="H35" s="6" t="s">
+      <c r="J35" s="6" t="s">
         <v>945</v>
       </c>
-      <c r="I35" s="6" t="s">
+      <c r="K35" s="6" t="s">
         <v>946</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>932</v>
-      </c>
-      <c r="K35" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -11373,19 +11372,19 @@
         <v>949</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>953</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I36" s="6" t="s">
         <v>950</v>
       </c>
-      <c r="H36" s="6" t="s">
+      <c r="J36" s="6" t="s">
         <v>951</v>
       </c>
-      <c r="I36" s="6" t="s">
+      <c r="K36" s="6" t="s">
         <v>952</v>
-      </c>
-      <c r="J36" s="6" t="s">
-        <v>953</v>
-      </c>
-      <c r="K36" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -11408,19 +11407,19 @@
         <v>955</v>
       </c>
       <c r="G37" s="6" t="s">
+        <v>953</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I37" s="6" t="s">
         <v>956</v>
       </c>
-      <c r="H37" s="6" t="s">
+      <c r="J37" s="6" t="s">
         <v>951</v>
       </c>
-      <c r="I37" s="6" t="s">
+      <c r="K37" s="6" t="s">
         <v>505</v>
-      </c>
-      <c r="J37" s="6" t="s">
-        <v>953</v>
-      </c>
-      <c r="K37" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -11443,19 +11442,19 @@
         <v>959</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>963</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I38" s="6" t="s">
         <v>960</v>
       </c>
-      <c r="H38" s="6" t="s">
+      <c r="J38" s="6" t="s">
         <v>961</v>
       </c>
-      <c r="I38" s="6" t="s">
+      <c r="K38" s="6" t="s">
         <v>962</v>
-      </c>
-      <c r="J38" s="6" t="s">
-        <v>963</v>
-      </c>
-      <c r="K38" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -11478,19 +11477,19 @@
         <v>965</v>
       </c>
       <c r="G39" s="6" t="s">
+        <v>963</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I39" s="6" t="s">
         <v>966</v>
       </c>
-      <c r="H39" s="6" t="s">
+      <c r="J39" s="6" t="s">
         <v>961</v>
       </c>
-      <c r="I39" s="6" t="s">
+      <c r="K39" s="6" t="s">
         <v>505</v>
-      </c>
-      <c r="J39" s="6" t="s">
-        <v>963</v>
-      </c>
-      <c r="K39" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -11513,19 +11512,19 @@
         <v>969</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>973</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I40" s="6" t="s">
         <v>970</v>
       </c>
-      <c r="H40" s="6" t="s">
+      <c r="J40" s="6" t="s">
         <v>971</v>
       </c>
-      <c r="I40" s="6" t="s">
+      <c r="K40" s="6" t="s">
         <v>972</v>
-      </c>
-      <c r="J40" s="6" t="s">
-        <v>973</v>
-      </c>
-      <c r="K40" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
@@ -11548,19 +11547,19 @@
         <v>975</v>
       </c>
       <c r="G41" s="6" t="s">
+        <v>973</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I41" s="6" t="s">
         <v>976</v>
       </c>
-      <c r="H41" s="6" t="s">
+      <c r="J41" s="6" t="s">
         <v>971</v>
       </c>
-      <c r="I41" s="6" t="s">
+      <c r="K41" s="6" t="s">
         <v>977</v>
-      </c>
-      <c r="J41" s="6" t="s">
-        <v>973</v>
-      </c>
-      <c r="K41" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
@@ -11583,19 +11582,19 @@
         <v>980</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>984</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I42" s="6" t="s">
         <v>981</v>
       </c>
-      <c r="H42" s="6" t="s">
+      <c r="J42" s="6" t="s">
         <v>982</v>
       </c>
-      <c r="I42" s="6" t="s">
+      <c r="K42" s="6" t="s">
         <v>983</v>
-      </c>
-      <c r="J42" s="6" t="s">
-        <v>984</v>
-      </c>
-      <c r="K42" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -11618,19 +11617,19 @@
         <v>986</v>
       </c>
       <c r="G43" s="6" t="s">
+        <v>984</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I43" s="6" t="s">
         <v>987</v>
       </c>
-      <c r="H43" s="6" t="s">
+      <c r="J43" s="6" t="s">
         <v>982</v>
       </c>
-      <c r="I43" s="6" t="s">
+      <c r="K43" s="6" t="s">
         <v>988</v>
-      </c>
-      <c r="J43" s="6" t="s">
-        <v>984</v>
-      </c>
-      <c r="K43" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -11653,19 +11652,19 @@
         <v>990</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>993</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I44" s="6" t="s">
         <v>991</v>
       </c>
-      <c r="H44" s="6" t="s">
+      <c r="J44" s="6" t="s">
         <v>982</v>
       </c>
-      <c r="I44" s="6" t="s">
+      <c r="K44" s="6" t="s">
         <v>992</v>
-      </c>
-      <c r="J44" s="6" t="s">
-        <v>993</v>
-      </c>
-      <c r="K44" s="4" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:11" ht="29" x14ac:dyDescent="0.35">
@@ -11688,22 +11687,22 @@
         <v>995</v>
       </c>
       <c r="G45" s="6" t="s">
+        <v>993</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I45" s="6" t="s">
         <v>996</v>
       </c>
-      <c r="H45" s="6" t="s">
+      <c r="J45" s="6" t="s">
         <v>997</v>
       </c>
-      <c r="I45" s="6" t="s">
+      <c r="K45" s="6" t="s">
         <v>998</v>
       </c>
-      <c r="J45" s="6" t="s">
-        <v>993</v>
-      </c>
-      <c r="K45" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="46" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>999</v>
       </c>
@@ -11723,22 +11722,22 @@
         <v>1001</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>1005</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I46" s="6" t="s">
         <v>1002</v>
       </c>
-      <c r="H46" s="6" t="s">
+      <c r="J46" s="6" t="s">
         <v>1003</v>
       </c>
-      <c r="I46" s="6" t="s">
+      <c r="K46" s="6" t="s">
         <v>1004</v>
       </c>
-      <c r="J46" s="6" t="s">
-        <v>1005</v>
-      </c>
-      <c r="K46" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>1006</v>
       </c>
@@ -11758,22 +11757,22 @@
         <v>1007</v>
       </c>
       <c r="G47" s="6" t="s">
+        <v>1005</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I47" s="6" t="s">
         <v>1008</v>
       </c>
-      <c r="H47" s="6" t="s">
+      <c r="J47" s="6" t="s">
         <v>1009</v>
       </c>
-      <c r="I47" s="6" t="s">
+      <c r="K47" s="6" t="s">
         <v>1010</v>
       </c>
-      <c r="J47" s="6" t="s">
-        <v>1005</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>1011</v>
       </c>
@@ -11793,22 +11792,22 @@
         <v>1012</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>1005</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I48" s="6" t="s">
         <v>1013</v>
       </c>
-      <c r="H48" s="6" t="s">
+      <c r="J48" s="6" t="s">
         <v>1003</v>
       </c>
-      <c r="I48" s="6" t="s">
+      <c r="K48" s="6" t="s">
         <v>1014</v>
       </c>
-      <c r="J48" s="6" t="s">
-        <v>1005</v>
-      </c>
-      <c r="K48" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="49" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>1015</v>
       </c>
@@ -11828,22 +11827,22 @@
         <v>1016</v>
       </c>
       <c r="G49" s="6" t="s">
+        <v>1005</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I49" s="6" t="s">
         <v>1017</v>
       </c>
-      <c r="H49" s="6" t="s">
+      <c r="J49" s="6" t="s">
         <v>1003</v>
       </c>
-      <c r="I49" s="6" t="s">
+      <c r="K49" s="6" t="s">
         <v>1018</v>
       </c>
-      <c r="J49" s="6" t="s">
-        <v>1005</v>
-      </c>
-      <c r="K49" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="50" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>1019</v>
       </c>
@@ -11863,22 +11862,22 @@
         <v>1021</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I50" s="6" t="s">
         <v>1022</v>
       </c>
-      <c r="H50" s="6" t="s">
+      <c r="J50" s="6" t="s">
         <v>1023</v>
       </c>
-      <c r="I50" s="6" t="s">
+      <c r="K50" s="6" t="s">
         <v>1024</v>
       </c>
-      <c r="J50" s="6" t="s">
-        <v>1025</v>
-      </c>
-      <c r="K50" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="51" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>1026</v>
       </c>
@@ -11898,22 +11897,22 @@
         <v>1027</v>
       </c>
       <c r="G51" s="6" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I51" s="6" t="s">
         <v>1028</v>
       </c>
-      <c r="H51" s="6" t="s">
+      <c r="J51" s="6" t="s">
         <v>1029</v>
       </c>
-      <c r="I51" s="6" t="s">
+      <c r="K51" s="6" t="s">
         <v>1030</v>
       </c>
-      <c r="J51" s="6" t="s">
-        <v>1025</v>
-      </c>
-      <c r="K51" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="52" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>1031</v>
       </c>
@@ -11933,22 +11932,22 @@
         <v>1032</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I52" s="6" t="s">
         <v>1033</v>
       </c>
-      <c r="H52" s="6" t="s">
+      <c r="J52" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="I52" s="6" t="s">
+      <c r="K52" s="6" t="s">
         <v>1034</v>
       </c>
-      <c r="J52" s="6" t="s">
-        <v>1025</v>
-      </c>
-      <c r="K52" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="53" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>1035</v>
       </c>
@@ -11968,22 +11967,22 @@
         <v>1036</v>
       </c>
       <c r="G53" s="6" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I53" s="6" t="s">
         <v>1037</v>
       </c>
-      <c r="H53" s="6" t="s">
+      <c r="J53" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="I53" s="6" t="s">
+      <c r="K53" s="6" t="s">
         <v>1038</v>
       </c>
-      <c r="J53" s="6" t="s">
-        <v>1025</v>
-      </c>
-      <c r="K53" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="54" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>1039</v>
       </c>
@@ -12003,22 +12002,22 @@
         <v>330</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I54" s="6" t="s">
         <v>1040</v>
       </c>
-      <c r="H54" s="6" t="s">
+      <c r="J54" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="I54" s="6" t="s">
+      <c r="K54" s="6" t="s">
         <v>1041</v>
       </c>
-      <c r="J54" s="6" t="s">
-        <v>1025</v>
-      </c>
-      <c r="K54" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="55" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>1042</v>
       </c>
@@ -12038,22 +12037,22 @@
         <v>1044</v>
       </c>
       <c r="G55" s="6" t="s">
+        <v>1048</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I55" s="6" t="s">
         <v>1045</v>
       </c>
-      <c r="H55" s="6" t="s">
+      <c r="J55" s="6" t="s">
         <v>1046</v>
       </c>
-      <c r="I55" s="6" t="s">
+      <c r="K55" s="6" t="s">
         <v>1047</v>
       </c>
-      <c r="J55" s="6" t="s">
-        <v>1048</v>
-      </c>
-      <c r="K55" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="56" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>1049</v>
       </c>
@@ -12073,22 +12072,22 @@
         <v>1050</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>1048</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I56" s="6" t="s">
         <v>1051</v>
       </c>
-      <c r="H56" s="6" t="s">
+      <c r="J56" s="6" t="s">
         <v>1052</v>
       </c>
-      <c r="I56" s="6" t="s">
+      <c r="K56" s="6" t="s">
         <v>1053</v>
       </c>
-      <c r="J56" s="6" t="s">
-        <v>1048</v>
-      </c>
-      <c r="K56" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="57" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>1054</v>
       </c>
@@ -12108,22 +12107,22 @@
         <v>1055</v>
       </c>
       <c r="G57" s="6" t="s">
+        <v>1048</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I57" s="6" t="s">
         <v>1056</v>
       </c>
-      <c r="H57" s="6" t="s">
+      <c r="J57" s="6" t="s">
         <v>1046</v>
       </c>
-      <c r="I57" s="6" t="s">
+      <c r="K57" s="6" t="s">
         <v>1057</v>
       </c>
-      <c r="J57" s="6" t="s">
-        <v>1048</v>
-      </c>
-      <c r="K57" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="58" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>1058</v>
       </c>
@@ -12143,22 +12142,22 @@
         <v>1059</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>1048</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I58" s="6" t="s">
         <v>1060</v>
       </c>
-      <c r="H58" s="6" t="s">
+      <c r="J58" s="6" t="s">
         <v>1046</v>
       </c>
-      <c r="I58" s="6" t="s">
+      <c r="K58" s="6" t="s">
         <v>1061</v>
       </c>
-      <c r="J58" s="6" t="s">
-        <v>1048</v>
-      </c>
-      <c r="K58" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="59" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>1062</v>
       </c>
@@ -12178,22 +12177,22 @@
         <v>1064</v>
       </c>
       <c r="G59" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I59" s="6" t="s">
         <v>1065</v>
       </c>
-      <c r="H59" s="6" t="s">
+      <c r="J59" s="6" t="s">
         <v>1066</v>
       </c>
-      <c r="I59" s="6" t="s">
+      <c r="K59" s="6" t="s">
         <v>1067</v>
       </c>
-      <c r="J59" s="6" t="s">
-        <v>1068</v>
-      </c>
-      <c r="K59" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="60" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>1069</v>
       </c>
@@ -12213,22 +12212,22 @@
         <v>1070</v>
       </c>
       <c r="G60" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I60" s="6" t="s">
         <v>1071</v>
       </c>
-      <c r="H60" s="6" t="s">
+      <c r="J60" s="6" t="s">
         <v>1072</v>
       </c>
-      <c r="I60" s="6" t="s">
+      <c r="K60" s="6" t="s">
         <v>1073</v>
       </c>
-      <c r="J60" s="6" t="s">
-        <v>1068</v>
-      </c>
-      <c r="K60" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="61" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>1074</v>
       </c>
@@ -12248,22 +12247,22 @@
         <v>1075</v>
       </c>
       <c r="G61" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I61" s="6" t="s">
         <v>1076</v>
       </c>
-      <c r="H61" s="6" t="s">
+      <c r="J61" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="I61" s="6" t="s">
+      <c r="K61" s="6" t="s">
         <v>1077</v>
       </c>
-      <c r="J61" s="6" t="s">
-        <v>1068</v>
-      </c>
-      <c r="K61" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="62" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
         <v>1078</v>
       </c>
@@ -12283,22 +12282,22 @@
         <v>1079</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I62" s="6" t="s">
         <v>1080</v>
       </c>
-      <c r="H62" s="6" t="s">
+      <c r="J62" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="I62" s="6" t="s">
+      <c r="K62" s="6" t="s">
         <v>1081</v>
       </c>
-      <c r="J62" s="6" t="s">
-        <v>1068</v>
-      </c>
-      <c r="K62" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="63" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
         <v>1082</v>
       </c>
@@ -12318,22 +12317,22 @@
         <v>330</v>
       </c>
       <c r="G63" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I63" s="6" t="s">
         <v>1083</v>
       </c>
-      <c r="H63" s="6" t="s">
+      <c r="J63" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="I63" s="6" t="s">
+      <c r="K63" s="6" t="s">
         <v>1084</v>
       </c>
-      <c r="J63" s="6" t="s">
-        <v>1068</v>
-      </c>
-      <c r="K63" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="64" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
         <v>1085</v>
       </c>
@@ -12353,22 +12352,22 @@
         <v>1087</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>1091</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I64" s="6" t="s">
         <v>1088</v>
       </c>
-      <c r="H64" s="6" t="s">
+      <c r="J64" s="6" t="s">
         <v>1089</v>
       </c>
-      <c r="I64" s="6" t="s">
+      <c r="K64" s="6" t="s">
         <v>1090</v>
       </c>
-      <c r="J64" s="6" t="s">
-        <v>1091</v>
-      </c>
-      <c r="K64" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="65" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
         <v>1092</v>
       </c>
@@ -12388,22 +12387,22 @@
         <v>1093</v>
       </c>
       <c r="G65" s="6" t="s">
+        <v>1091</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I65" s="6" t="s">
         <v>1094</v>
       </c>
-      <c r="H65" s="6" t="s">
+      <c r="J65" s="6" t="s">
         <v>1095</v>
       </c>
-      <c r="I65" s="6" t="s">
+      <c r="K65" s="6" t="s">
         <v>1096</v>
       </c>
-      <c r="J65" s="6" t="s">
-        <v>1091</v>
-      </c>
-      <c r="K65" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="66" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>1097</v>
       </c>
@@ -12423,22 +12422,22 @@
         <v>1098</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>1091</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I66" s="6" t="s">
         <v>1094</v>
       </c>
-      <c r="H66" s="6" t="s">
+      <c r="J66" s="6" t="s">
         <v>1099</v>
       </c>
-      <c r="I66" s="6" t="s">
+      <c r="K66" s="6" t="s">
         <v>1100</v>
       </c>
-      <c r="J66" s="6" t="s">
-        <v>1091</v>
-      </c>
-      <c r="K66" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="67" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
         <v>1101</v>
       </c>
@@ -12458,22 +12457,22 @@
         <v>1102</v>
       </c>
       <c r="G67" s="6" t="s">
+        <v>1091</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I67" s="6" t="s">
         <v>1103</v>
       </c>
-      <c r="H67" s="6" t="s">
+      <c r="J67" s="6" t="s">
         <v>1104</v>
       </c>
-      <c r="I67" s="6" t="s">
+      <c r="K67" s="6" t="s">
         <v>1105</v>
       </c>
-      <c r="J67" s="6" t="s">
-        <v>1091</v>
-      </c>
-      <c r="K67" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="68" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
         <v>1106</v>
       </c>
@@ -12493,22 +12492,22 @@
         <v>1107</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>1091</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I68" s="6" t="s">
         <v>1108</v>
       </c>
-      <c r="H68" s="6" t="s">
+      <c r="J68" s="6" t="s">
         <v>1109</v>
       </c>
-      <c r="I68" s="6" t="s">
+      <c r="K68" s="6" t="s">
         <v>1110</v>
       </c>
-      <c r="J68" s="6" t="s">
-        <v>1091</v>
-      </c>
-      <c r="K68" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="69" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
         <v>1111</v>
       </c>
@@ -12528,22 +12527,22 @@
         <v>1113</v>
       </c>
       <c r="G69" s="6" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I69" s="6" t="s">
         <v>1114</v>
       </c>
-      <c r="H69" s="6" t="s">
+      <c r="J69" s="6" t="s">
         <v>1115</v>
       </c>
-      <c r="I69" s="6" t="s">
+      <c r="K69" s="6" t="s">
         <v>1116</v>
       </c>
-      <c r="J69" s="6" t="s">
-        <v>1117</v>
-      </c>
-      <c r="K69" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="70" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
         <v>1118</v>
       </c>
@@ -12563,22 +12562,22 @@
         <v>1119</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I70" s="6" t="s">
         <v>1120</v>
       </c>
-      <c r="H70" s="6" t="s">
+      <c r="J70" s="6" t="s">
         <v>1121</v>
       </c>
-      <c r="I70" s="6" t="s">
+      <c r="K70" s="6" t="s">
         <v>1122</v>
       </c>
-      <c r="J70" s="6" t="s">
-        <v>1117</v>
-      </c>
-      <c r="K70" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="71" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
         <v>1123</v>
       </c>
@@ -12598,22 +12597,22 @@
         <v>1124</v>
       </c>
       <c r="G71" s="6" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I71" s="6" t="s">
         <v>1125</v>
       </c>
-      <c r="H71" s="6" t="s">
+      <c r="J71" s="6" t="s">
         <v>1126</v>
       </c>
-      <c r="I71" s="6" t="s">
+      <c r="K71" s="6" t="s">
         <v>1127</v>
       </c>
-      <c r="J71" s="6" t="s">
-        <v>1117</v>
-      </c>
-      <c r="K71" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="72" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
         <v>1128</v>
       </c>
@@ -12633,22 +12632,22 @@
         <v>1129</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I72" s="6" t="s">
         <v>1130</v>
       </c>
-      <c r="H72" s="6" t="s">
+      <c r="J72" s="6" t="s">
         <v>1131</v>
       </c>
-      <c r="I72" s="6" t="s">
+      <c r="K72" s="6" t="s">
         <v>1132</v>
       </c>
-      <c r="J72" s="6" t="s">
-        <v>1117</v>
-      </c>
-      <c r="K72" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="73" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
         <v>1133</v>
       </c>
@@ -12668,22 +12667,22 @@
         <v>1134</v>
       </c>
       <c r="G73" s="6" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I73" s="6" t="s">
         <v>1135</v>
       </c>
-      <c r="H73" s="6" t="s">
+      <c r="J73" s="6" t="s">
         <v>1136</v>
       </c>
-      <c r="I73" s="6" t="s">
+      <c r="K73" s="6" t="s">
         <v>1137</v>
       </c>
-      <c r="J73" s="6" t="s">
-        <v>1117</v>
-      </c>
-      <c r="K73" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="74" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
         <v>1138</v>
       </c>
@@ -12703,22 +12702,22 @@
         <v>1140</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>1144</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I74" s="6" t="s">
         <v>1141</v>
       </c>
-      <c r="H74" s="6" t="s">
+      <c r="J74" s="6" t="s">
         <v>1142</v>
       </c>
-      <c r="I74" s="6" t="s">
+      <c r="K74" s="6" t="s">
         <v>1143</v>
       </c>
-      <c r="J74" s="6" t="s">
-        <v>1144</v>
-      </c>
-      <c r="K74" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="75" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
         <v>1145</v>
       </c>
@@ -12738,22 +12737,22 @@
         <v>1146</v>
       </c>
       <c r="G75" s="6" t="s">
+        <v>1144</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I75" s="6" t="s">
         <v>1141</v>
       </c>
-      <c r="H75" s="6" t="s">
+      <c r="J75" s="6" t="s">
         <v>1147</v>
       </c>
-      <c r="I75" s="6" t="s">
+      <c r="K75" s="6" t="s">
         <v>1148</v>
       </c>
-      <c r="J75" s="6" t="s">
-        <v>1144</v>
-      </c>
-      <c r="K75" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="76" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
         <v>1149</v>
       </c>
@@ -12773,22 +12772,22 @@
         <v>1150</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>1144</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I76" s="6" t="s">
         <v>1151</v>
       </c>
-      <c r="H76" s="6" t="s">
+      <c r="J76" s="6" t="s">
         <v>1152</v>
       </c>
-      <c r="I76" s="6" t="s">
+      <c r="K76" s="6" t="s">
         <v>1153</v>
       </c>
-      <c r="J76" s="6" t="s">
-        <v>1144</v>
-      </c>
-      <c r="K76" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="77" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
         <v>1154</v>
       </c>
@@ -12808,22 +12807,22 @@
         <v>1155</v>
       </c>
       <c r="G77" s="6" t="s">
+        <v>1144</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I77" s="6" t="s">
         <v>1156</v>
       </c>
-      <c r="H77" s="6" t="s">
+      <c r="J77" s="6" t="s">
         <v>1157</v>
       </c>
-      <c r="I77" s="6" t="s">
+      <c r="K77" s="6" t="s">
         <v>1158</v>
       </c>
-      <c r="J77" s="6" t="s">
-        <v>1144</v>
-      </c>
-      <c r="K77" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="78" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
         <v>1159</v>
       </c>
@@ -12843,22 +12842,22 @@
         <v>1160</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>1144</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I78" s="6" t="s">
         <v>1161</v>
       </c>
-      <c r="H78" s="6" t="s">
+      <c r="J78" s="6" t="s">
         <v>1136</v>
       </c>
-      <c r="I78" s="6" t="s">
+      <c r="K78" s="6" t="s">
         <v>1162</v>
       </c>
-      <c r="J78" s="6" t="s">
-        <v>1144</v>
-      </c>
-      <c r="K78" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="79" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
         <v>1163</v>
       </c>
@@ -12878,22 +12877,22 @@
         <v>1164</v>
       </c>
       <c r="G79" s="6" t="s">
+        <v>1144</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I79" s="6" t="s">
         <v>1165</v>
       </c>
-      <c r="H79" s="6" t="s">
+      <c r="J79" s="6" t="s">
         <v>1136</v>
       </c>
-      <c r="I79" s="6" t="s">
+      <c r="K79" s="6" t="s">
         <v>1166</v>
       </c>
-      <c r="J79" s="6" t="s">
-        <v>1144</v>
-      </c>
-      <c r="K79" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="80" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
         <v>1167</v>
       </c>
@@ -12913,22 +12912,22 @@
         <v>1168</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>1144</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I80" s="6" t="s">
         <v>1169</v>
       </c>
-      <c r="H80" s="6" t="s">
+      <c r="J80" s="6" t="s">
         <v>1136</v>
       </c>
-      <c r="I80" s="6" t="s">
+      <c r="K80" s="6" t="s">
         <v>1170</v>
       </c>
-      <c r="J80" s="6" t="s">
-        <v>1144</v>
-      </c>
-      <c r="K80" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="81" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
         <v>1171</v>
       </c>
@@ -12948,22 +12947,22 @@
         <v>1173</v>
       </c>
       <c r="G81" s="6" t="s">
+        <v>1177</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I81" s="6" t="s">
         <v>1174</v>
       </c>
-      <c r="H81" s="6" t="s">
+      <c r="J81" s="6" t="s">
         <v>1175</v>
       </c>
-      <c r="I81" s="6" t="s">
+      <c r="K81" s="6" t="s">
         <v>1176</v>
       </c>
-      <c r="J81" s="6" t="s">
-        <v>1177</v>
-      </c>
-      <c r="K81" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="82" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
         <v>1178</v>
       </c>
@@ -12983,22 +12982,22 @@
         <v>1179</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>1177</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I82" s="6" t="s">
         <v>1180</v>
       </c>
-      <c r="H82" s="6" t="s">
+      <c r="J82" s="6" t="s">
         <v>1181</v>
       </c>
-      <c r="I82" s="6" t="s">
+      <c r="K82" s="6" t="s">
         <v>1182</v>
       </c>
-      <c r="J82" s="6" t="s">
-        <v>1177</v>
-      </c>
-      <c r="K82" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="83" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
         <v>1183</v>
       </c>
@@ -13018,22 +13017,22 @@
         <v>1184</v>
       </c>
       <c r="G83" s="6" t="s">
+        <v>1177</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I83" s="6" t="s">
         <v>1174</v>
       </c>
-      <c r="H83" s="6" t="s">
+      <c r="J83" s="6" t="s">
         <v>1185</v>
       </c>
-      <c r="I83" s="6" t="s">
+      <c r="K83" s="6" t="s">
         <v>1186</v>
       </c>
-      <c r="J83" s="6" t="s">
-        <v>1177</v>
-      </c>
-      <c r="K83" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="84" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
         <v>1187</v>
       </c>
@@ -13053,22 +13052,22 @@
         <v>1188</v>
       </c>
       <c r="G84" s="6" t="s">
+        <v>1177</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I84" s="6" t="s">
         <v>1189</v>
       </c>
-      <c r="H84" s="6" t="s">
+      <c r="J84" s="6" t="s">
         <v>1136</v>
       </c>
-      <c r="I84" s="6" t="s">
+      <c r="K84" s="6" t="s">
         <v>1190</v>
       </c>
-      <c r="J84" s="6" t="s">
-        <v>1177</v>
-      </c>
-      <c r="K84" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="85" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
         <v>1191</v>
       </c>
@@ -13088,22 +13087,22 @@
         <v>1192</v>
       </c>
       <c r="G85" s="6" t="s">
+        <v>1177</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I85" s="6" t="s">
         <v>1193</v>
       </c>
-      <c r="H85" s="6" t="s">
+      <c r="J85" s="6" t="s">
         <v>1136</v>
       </c>
-      <c r="I85" s="6" t="s">
+      <c r="K85" s="6" t="s">
         <v>1194</v>
       </c>
-      <c r="J85" s="6" t="s">
-        <v>1177</v>
-      </c>
-      <c r="K85" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="86" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
         <v>1195</v>
       </c>
@@ -13123,22 +13122,22 @@
         <v>1196</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>1177</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I86" s="6" t="s">
         <v>1197</v>
       </c>
-      <c r="H86" s="6" t="s">
+      <c r="J86" s="6" t="s">
         <v>1136</v>
       </c>
-      <c r="I86" s="6" t="s">
+      <c r="K86" s="6" t="s">
         <v>1198</v>
       </c>
-      <c r="J86" s="6" t="s">
-        <v>1177</v>
-      </c>
-      <c r="K86" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="87" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
         <v>1199</v>
       </c>
@@ -13158,22 +13157,22 @@
         <v>1201</v>
       </c>
       <c r="G87" s="6" t="s">
+        <v>1205</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I87" s="6" t="s">
         <v>1202</v>
       </c>
-      <c r="H87" s="6" t="s">
+      <c r="J87" s="6" t="s">
         <v>1203</v>
       </c>
-      <c r="I87" s="6" t="s">
+      <c r="K87" s="6" t="s">
         <v>1204</v>
       </c>
-      <c r="J87" s="6" t="s">
-        <v>1205</v>
-      </c>
-      <c r="K87" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="88" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
         <v>1206</v>
       </c>
@@ -13193,22 +13192,22 @@
         <v>1207</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>1205</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I88" s="6" t="s">
         <v>1208</v>
       </c>
-      <c r="H88" s="6" t="s">
+      <c r="J88" s="6" t="s">
         <v>1209</v>
       </c>
-      <c r="I88" s="6" t="s">
+      <c r="K88" s="6" t="s">
         <v>1210</v>
       </c>
-      <c r="J88" s="6" t="s">
-        <v>1205</v>
-      </c>
-      <c r="K88" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="89" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
         <v>1211</v>
       </c>
@@ -13228,22 +13227,22 @@
         <v>1212</v>
       </c>
       <c r="G89" s="6" t="s">
+        <v>1205</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I89" s="6" t="s">
         <v>1213</v>
       </c>
-      <c r="H89" s="6" t="s">
+      <c r="J89" s="6" t="s">
         <v>1209</v>
       </c>
-      <c r="I89" s="6" t="s">
+      <c r="K89" s="6" t="s">
         <v>1214</v>
       </c>
-      <c r="J89" s="6" t="s">
-        <v>1205</v>
-      </c>
-      <c r="K89" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="90" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
         <v>1215</v>
       </c>
@@ -13263,22 +13262,22 @@
         <v>1216</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>1205</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I90" s="6" t="s">
         <v>1217</v>
       </c>
-      <c r="H90" s="6" t="s">
+      <c r="J90" s="6" t="s">
         <v>1209</v>
       </c>
-      <c r="I90" s="6" t="s">
+      <c r="K90" s="6" t="s">
         <v>1218</v>
       </c>
-      <c r="J90" s="6" t="s">
-        <v>1205</v>
-      </c>
-      <c r="K90" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="91" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
         <v>1219</v>
       </c>
@@ -13298,22 +13297,22 @@
         <v>1220</v>
       </c>
       <c r="G91" s="6" t="s">
+        <v>1205</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I91" s="6" t="s">
         <v>1221</v>
       </c>
-      <c r="H91" s="6" t="s">
+      <c r="J91" s="6" t="s">
         <v>1209</v>
       </c>
-      <c r="I91" s="6" t="s">
+      <c r="K91" s="6" t="s">
         <v>1222</v>
       </c>
-      <c r="J91" s="6" t="s">
-        <v>1205</v>
-      </c>
-      <c r="K91" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
         <v>1223</v>
       </c>
@@ -13333,22 +13332,22 @@
         <v>1224</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>1205</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I92" s="6" t="s">
         <v>1225</v>
       </c>
-      <c r="H92" s="6" t="s">
+      <c r="J92" s="6" t="s">
         <v>1209</v>
       </c>
-      <c r="I92" s="6" t="s">
+      <c r="K92" s="6" t="s">
         <v>1226</v>
       </c>
-      <c r="J92" s="6" t="s">
-        <v>1205</v>
-      </c>
-      <c r="K92" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="93" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
         <v>1227</v>
       </c>
@@ -13368,22 +13367,22 @@
         <v>1229</v>
       </c>
       <c r="G93" s="6" t="s">
+        <v>1233</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I93" s="6" t="s">
         <v>1230</v>
       </c>
-      <c r="H93" s="6" t="s">
+      <c r="J93" s="6" t="s">
         <v>1231</v>
       </c>
-      <c r="I93" s="6" t="s">
+      <c r="K93" s="6" t="s">
         <v>1232</v>
       </c>
-      <c r="J93" s="6" t="s">
-        <v>1233</v>
-      </c>
-      <c r="K93" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="94" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
         <v>1234</v>
       </c>
@@ -13403,22 +13402,22 @@
         <v>1235</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>1233</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I94" s="6" t="s">
         <v>1236</v>
       </c>
-      <c r="H94" s="6" t="s">
+      <c r="J94" s="6" t="s">
         <v>1237</v>
       </c>
-      <c r="I94" s="6" t="s">
+      <c r="K94" s="6" t="s">
         <v>1238</v>
       </c>
-      <c r="J94" s="6" t="s">
-        <v>1233</v>
-      </c>
-      <c r="K94" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="95" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
         <v>1239</v>
       </c>
@@ -13438,22 +13437,22 @@
         <v>1240</v>
       </c>
       <c r="G95" s="6" t="s">
+        <v>1233</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I95" s="6" t="s">
         <v>1241</v>
       </c>
-      <c r="H95" s="6" t="s">
+      <c r="J95" s="6" t="s">
         <v>1242</v>
       </c>
-      <c r="I95" s="6" t="s">
+      <c r="K95" s="6" t="s">
         <v>1243</v>
       </c>
-      <c r="J95" s="6" t="s">
-        <v>1233</v>
-      </c>
-      <c r="K95" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="96" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
         <v>1244</v>
       </c>
@@ -13473,22 +13472,22 @@
         <v>1245</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>1233</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I96" s="6" t="s">
         <v>1246</v>
       </c>
-      <c r="H96" s="6" t="s">
+      <c r="J96" s="6" t="s">
         <v>1247</v>
       </c>
-      <c r="I96" s="6" t="s">
+      <c r="K96" s="6" t="s">
         <v>1248</v>
       </c>
-      <c r="J96" s="6" t="s">
-        <v>1233</v>
-      </c>
-      <c r="K96" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="97" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
         <v>1249</v>
       </c>
@@ -13508,22 +13507,22 @@
         <v>1251</v>
       </c>
       <c r="G97" s="6" t="s">
+        <v>1255</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I97" s="6" t="s">
         <v>1252</v>
       </c>
-      <c r="H97" s="6" t="s">
+      <c r="J97" s="6" t="s">
         <v>1253</v>
       </c>
-      <c r="I97" s="6" t="s">
+      <c r="K97" s="6" t="s">
         <v>1254</v>
       </c>
-      <c r="J97" s="6" t="s">
-        <v>1255</v>
-      </c>
-      <c r="K97" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="98" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
         <v>1256</v>
       </c>
@@ -13543,29 +13542,23 @@
         <v>1257</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>1255</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I98" s="6" t="s">
         <v>1258</v>
       </c>
-      <c r="H98" s="6" t="s">
+      <c r="J98" s="6" t="s">
         <v>1259</v>
       </c>
-      <c r="I98" s="6" t="s">
+      <c r="K98" s="6" t="s">
         <v>1260</v>
       </c>
-      <c r="J98" s="6" t="s">
-        <v>1255</v>
-      </c>
-      <c r="K98" s="4" t="s">
-        <v>40</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K98" xr:uid="{00000000-0009-0000-0000-000006000000}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="Integration"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:K98" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>